--- a/SuppXLS/Scen_InputsBiogPlant.xlsx
+++ b/SuppXLS/Scen_InputsBiogPlant.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patir\Documents\Praca ESMlab\1. TIMES-PL-PSE\2026\2. AGR_model_wyizolowany\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patir\Documents\Praca ESMlab\1. TIMES-PL-PSE\1. 2026\2. AGR_model_wyizolowany\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1555BA4-DD4C-4A63-B1C1-C1C118AFF6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE8AF25-E850-4469-AED4-C302CFB71A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7515,25 +7515,25 @@
         <v>1</v>
       </c>
       <c r="G27" s="30">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H27" s="30">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I27" s="30">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J27" s="30">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K27" s="30">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L27" s="30">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M27" s="30">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N27" s="25">
         <v>5</v>
@@ -7951,26 +7951,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A7D98A4600D5044F9F854C890D6CC50E" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3a89f9027361f7d3c140af2fe110eadb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8acd6055-54fc-4ce7-b3df-0a09834a0329" xmlns:ns3="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff995f4215d3ca90fb464d6ddf93df71" ns2:_="" ns3:_="">
     <xsd:import namespace="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
@@ -8213,26 +8193,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31CAF8EB-1589-42DD-BC0B-7BF2AA67CCF9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
-    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A411E4B2-5D3D-4AF5-AF43-FAF4CEAEDF56}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD4F0E47-7F06-4CD3-9EF5-74801E072FF2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8249,4 +8230,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A411E4B2-5D3D-4AF5-AF43-FAF4CEAEDF56}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31CAF8EB-1589-42DD-BC0B-7BF2AA67CCF9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
+    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/SuppXLS/Scen_InputsBiogPlant.xlsx
+++ b/SuppXLS/Scen_InputsBiogPlant.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patir\Documents\Praca ESMlab\1. TIMES-PL-PSE\1. 2026\2. AGR_model_wyizolowany\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aghedupl.sharepoint.com/sites/TIMES-PL-PSE/Shared Documents/General/MODELE/2026/AGR_wyizolowany/SuppXLS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE8AF25-E850-4469-AED4-C302CFB71A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="202" documentId="13_ncr:1_{D1555BA4-DD4C-4A63-B1C1-C1C118AFF6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D773A174-B533-4A50-B989-C00D416BF573}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UCT1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="71">
   <si>
     <t>~UC_Sets: R_E: AllRegions</t>
   </si>
@@ -92,9 +92,6 @@
     <t>AGR_LIV_MANURE_CAT_NON-DAIRY</t>
   </si>
   <si>
-    <t>UC_RHSRTS~2020</t>
-  </si>
-  <si>
     <t>UC_RHSRTS~2025</t>
   </si>
   <si>
@@ -126,9 +123,6 @@
   </si>
   <si>
     <t>Opis ograniczenia użytkownika</t>
-  </si>
-  <si>
-    <t>LO</t>
   </si>
   <si>
     <t>Agriculture Manure Fed Biogass</t>
@@ -230,20 +224,35 @@
     <t>UC_RHSRTS~2050</t>
   </si>
   <si>
-    <t>AGR_EX_BIOG</t>
-  </si>
-  <si>
     <t>~UC_T</t>
   </si>
   <si>
-    <t>Wymagany minimalny wsad substratu do produkcji biogazu [kt]</t>
+    <t>Produkcja odpadów maks. [kt] (zebranych)</t>
+  </si>
+  <si>
+    <t>UC_RHSRTS~2024</t>
+  </si>
+  <si>
+    <t>Ścieżki rozwoju [%]</t>
+  </si>
+  <si>
+    <t>do ustawiania</t>
+  </si>
+  <si>
+    <t>UP</t>
+  </si>
+  <si>
+    <t>Wymagany minimalny wsad substratu do produkcji biometanu [kt]</t>
+  </si>
+  <si>
+    <t>AGR_NEW_BIOG_MAN,AGR_NEW_BIOG_MIX,AGR_NEW_BIOG_LIGN,AGR_NEW_BIO_CH4_MAN,AGR_NEW_BIO_CH4_MIX,AGR_NEW_BIO_CH4_LIGN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="27">
+  <numFmts count="28">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;zł&quot;_-;\-* #,##0.00\ &quot;zł&quot;_-;_-* &quot;-&quot;??\ &quot;zł&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
@@ -271,6 +280,7 @@
     <numFmt numFmtId="185" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="186" formatCode="_ &quot;kr&quot;\ * #,##0_ ;_ &quot;kr&quot;\ * \-#,##0_ ;_ &quot;kr&quot;\ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="187" formatCode="_ &quot;kr&quot;\ * #,##0.00_ ;_ &quot;kr&quot;\ * \-#,##0.00_ ;_ &quot;kr&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="188" formatCode="0.0%"/>
   </numFmts>
   <fonts count="119">
     <font>
@@ -1338,12 +1348,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1582,6 +1592,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2182">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -4107,7 +4128,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="115" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4142,13 +4163,29 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="14" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="14" borderId="0" xfId="1131" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2181" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="52" borderId="0" xfId="2181" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="1131" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="53" borderId="0" xfId="1131" applyFill="1"/>
     <xf numFmtId="3" fontId="16" fillId="5" borderId="0" xfId="1133" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="52" borderId="0" xfId="1131" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="2181" applyFont="1" applyFill="1"/>
+    <xf numFmtId="188" fontId="0" fillId="53" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="52" borderId="0" xfId="2181" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="16" fillId="13" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2182">
@@ -5216,6 +5253,7 @@
     <cellStyle name="Neutralne 9_COM_BND" xfId="1079" xr:uid="{6A2CB00B-A082-4E91-9034-E18742ED0AD0}"/>
     <cellStyle name="Neutralne_CHP" xfId="1080" xr:uid="{D4B1577A-56D8-4830-B45D-ACB712881634}"/>
     <cellStyle name="no dec" xfId="1081" xr:uid="{05A6E796-705C-459C-9083-31C5C2B501A7}"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal - Style1" xfId="1082" xr:uid="{422DB56D-DE92-449A-A73B-E02EC79F0146}"/>
     <cellStyle name="Normal - Style1 2 2 3" xfId="14" xr:uid="{DC545E0B-E419-471E-892E-F5E9CBF5B7CC}"/>
     <cellStyle name="Normal - Style1 2 2 3 2" xfId="2168" xr:uid="{B3B665C3-72E1-4DCC-90DC-397510F65D65}"/>
@@ -5289,7 +5327,6 @@
     <cellStyle name="Normal GHG-Shade 2" xfId="1129" xr:uid="{332E491B-28EA-478D-8837-B4DC72CD947A}"/>
     <cellStyle name="Normale_B2020" xfId="1130" xr:uid="{BBE33778-D881-4D14-9174-CBFFF9C5A0A1}"/>
     <cellStyle name="Normale_Scen_UC_IND-StrucConst" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
     <cellStyle name="Normalny 10" xfId="1132" xr:uid="{7BEE2132-44C2-4E67-A38F-4476F86FD93C}"/>
     <cellStyle name="Normalny 10 10" xfId="11" xr:uid="{3C7998C5-C4B0-42D6-B1DA-0233E04A4AA3}"/>
     <cellStyle name="Normalny 10 10 2" xfId="2167" xr:uid="{A7EB448A-69A2-4460-B07D-C674E4A16132}"/>
@@ -6667,7 +6704,7 @@
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Pakiet Office 2007–2010">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6705,7 +6742,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Pakiet Office 2007–2010">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -6777,7 +6814,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Pakiet Office 2007–2010">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6951,10 +6988,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:S84"/>
+  <dimension ref="A1:AA84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="3" width="22.42578125" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" customWidth="1"/>
+    <col min="3" max="3" width="74.42578125" customWidth="1"/>
     <col min="4" max="4" width="37.28515625" customWidth="1"/>
     <col min="7" max="7" width="11.28515625" customWidth="1"/>
     <col min="8" max="8" width="12.28515625" customWidth="1"/>
@@ -6962,7 +7000,7 @@
     <col min="10" max="13" width="12" customWidth="1"/>
     <col min="15" max="15" width="26.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
@@ -7030,7 +7068,7 @@
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E14" s="19"/>
       <c r="F14" s="19"/>
@@ -7087,12 +7125,12 @@
       <c r="Q16" s="13"/>
       <c r="R16" s="13"/>
     </row>
-    <row r="17" spans="2:18">
+    <row r="17" spans="2:27">
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
       <c r="E17" s="18" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="17"/>
@@ -7108,7 +7146,7 @@
       <c r="Q17" s="13"/>
       <c r="R17" s="13"/>
     </row>
-    <row r="18" spans="2:18" ht="25.5">
+    <row r="18" spans="2:27" ht="25.5">
       <c r="B18" s="21" t="s">
         <v>1</v>
       </c>
@@ -7125,28 +7163,28 @@
         <v>9</v>
       </c>
       <c r="G18" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="H18" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="22" t="s">
+      <c r="I18" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="22" t="s">
+      <c r="J18" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="M18" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="N18" s="22" t="s">
         <v>21</v>
-      </c>
-      <c r="J18" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="K18" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="L18" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="M18" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="N18" s="22" t="s">
-        <v>22</v>
       </c>
       <c r="O18" s="21" t="s">
         <v>13</v>
@@ -7154,577 +7192,1004 @@
       <c r="P18" s="13"/>
       <c r="Q18" s="13"/>
       <c r="R18" s="13"/>
+      <c r="S18" s="30"/>
+      <c r="T18" s="30"/>
+      <c r="U18" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="V18" s="39"/>
+      <c r="W18" s="39"/>
+      <c r="X18" s="39"/>
+      <c r="Y18" s="39"/>
+      <c r="Z18" s="39"/>
+      <c r="AA18" s="39"/>
     </row>
-    <row r="19" spans="2:18" ht="63.75">
+    <row r="19" spans="2:27" ht="63.75">
       <c r="B19" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="D19" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="23" t="s">
+      <c r="E19" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="E19" s="23" t="s">
+      <c r="F19" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="F19" s="23" t="s">
+      <c r="G19" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="G19" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
       <c r="J19" s="23"/>
       <c r="K19" s="23"/>
       <c r="L19" s="23"/>
       <c r="M19" s="23"/>
       <c r="N19" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="O19" s="23" t="s">
         <v>29</v>
-      </c>
-      <c r="O19" s="23" t="s">
-        <v>30</v>
       </c>
       <c r="P19" s="13"/>
       <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
+      <c r="S19" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="T19" s="32"/>
+      <c r="U19" s="33">
+        <v>2024</v>
+      </c>
+      <c r="V19" s="33">
+        <v>2025</v>
+      </c>
+      <c r="W19" s="33">
+        <v>2030</v>
+      </c>
+      <c r="X19" s="33">
+        <v>2035</v>
+      </c>
+      <c r="Y19" s="33">
+        <v>2040</v>
+      </c>
+      <c r="Z19" s="33">
+        <v>2045</v>
+      </c>
+      <c r="AA19" s="33">
+        <v>2050</v>
+      </c>
     </row>
-    <row r="20" spans="2:18" ht="24" customHeight="1">
+    <row r="20" spans="2:27" ht="39.75" customHeight="1">
       <c r="B20" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" t="s">
-        <v>65</v>
-      </c>
-      <c r="D20" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="E20" s="28" t="s">
-        <v>31</v>
+        <v>39</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>68</v>
       </c>
       <c r="F20" s="25">
         <v>1</v>
       </c>
-      <c r="G20" s="30">
-        <v>10</v>
-      </c>
-      <c r="H20" s="30">
-        <v>10</v>
-      </c>
-      <c r="I20" s="30">
-        <v>10</v>
-      </c>
-      <c r="J20" s="30">
-        <v>10</v>
-      </c>
-      <c r="K20" s="30">
-        <v>10</v>
-      </c>
-      <c r="L20" s="30">
-        <v>10</v>
-      </c>
-      <c r="M20" s="30">
-        <v>10</v>
+      <c r="G20" s="28">
+        <f t="shared" ref="G20:M20" si="0">$S$20*U20</f>
+        <v>36.461650536299999</v>
+      </c>
+      <c r="H20" s="28">
+        <f t="shared" si="0"/>
+        <v>54.692475804449998</v>
+      </c>
+      <c r="I20" s="28">
+        <f t="shared" si="0"/>
+        <v>820.38713706675003</v>
+      </c>
+      <c r="J20" s="28">
+        <f t="shared" si="0"/>
+        <v>1002.69538974825</v>
+      </c>
+      <c r="K20" s="28">
+        <f t="shared" si="0"/>
+        <v>1185.00364242975</v>
+      </c>
+      <c r="L20" s="28">
+        <f t="shared" si="0"/>
+        <v>1276.1577687704998</v>
+      </c>
+      <c r="M20" s="28">
+        <f t="shared" si="0"/>
+        <v>1367.3118951112499</v>
       </c>
       <c r="N20" s="25">
         <v>5</v>
       </c>
       <c r="O20" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="S20" s="34">
+        <v>1823.0825268149999</v>
+      </c>
+      <c r="T20" s="34"/>
+      <c r="U20" s="36">
+        <v>0.02</v>
+      </c>
+      <c r="V20" s="36">
+        <v>0.03</v>
+      </c>
+      <c r="W20" s="36">
+        <v>0.45</v>
+      </c>
+      <c r="X20" s="36">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="Y20" s="36">
+        <v>0.65</v>
+      </c>
+      <c r="Z20" s="36">
+        <v>0.7</v>
+      </c>
+      <c r="AA20" s="36">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="21" spans="2:27" ht="39.75" customHeight="1">
+      <c r="B21" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="35" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="21" spans="2:18">
-      <c r="B21" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="E21" s="28" t="s">
-        <v>31</v>
+      <c r="E21" s="27" t="s">
+        <v>68</v>
       </c>
       <c r="F21" s="25">
         <v>1</v>
       </c>
-      <c r="G21" s="30">
-        <v>10</v>
-      </c>
-      <c r="H21" s="30">
-        <v>10</v>
-      </c>
-      <c r="I21" s="30">
-        <v>10</v>
-      </c>
-      <c r="J21" s="30">
-        <v>10</v>
-      </c>
-      <c r="K21" s="30">
-        <v>10</v>
-      </c>
-      <c r="L21" s="30">
-        <v>10</v>
-      </c>
-      <c r="M21" s="30">
-        <v>10</v>
+      <c r="G21" s="28">
+        <f t="shared" ref="G21:M21" si="1">$S$21*U21</f>
+        <v>7.9626655680000002</v>
+      </c>
+      <c r="H21" s="28">
+        <f t="shared" si="1"/>
+        <v>11.943998351999999</v>
+      </c>
+      <c r="I21" s="28">
+        <f t="shared" si="1"/>
+        <v>159.25331136</v>
+      </c>
+      <c r="J21" s="28">
+        <f t="shared" si="1"/>
+        <v>199.0666392</v>
+      </c>
+      <c r="K21" s="28">
+        <f t="shared" si="1"/>
+        <v>238.87996704</v>
+      </c>
+      <c r="L21" s="28">
+        <f t="shared" si="1"/>
+        <v>258.78663096000002</v>
+      </c>
+      <c r="M21" s="28">
+        <f t="shared" si="1"/>
+        <v>278.69329488</v>
       </c>
       <c r="N21" s="25">
         <v>5</v>
       </c>
       <c r="O21" s="25" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="S21" s="34">
+        <v>398.13327839999999</v>
+      </c>
+      <c r="T21" s="34"/>
+      <c r="U21" s="36">
+        <v>0.02</v>
+      </c>
+      <c r="V21" s="36">
+        <v>0.03</v>
+      </c>
+      <c r="W21" s="36">
+        <v>0.4</v>
+      </c>
+      <c r="X21" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="Y21" s="36">
+        <v>0.6</v>
+      </c>
+      <c r="Z21" s="36">
+        <v>0.65</v>
+      </c>
+      <c r="AA21" s="36">
+        <v>0.7</v>
       </c>
     </row>
-    <row r="22" spans="2:18">
+    <row r="22" spans="2:27" ht="39.75" customHeight="1">
       <c r="B22" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" t="s">
-        <v>65</v>
-      </c>
-      <c r="D22" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="E22" s="29" t="s">
-        <v>31</v>
+        <v>49</v>
+      </c>
+      <c r="C22" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="27" t="s">
+        <v>68</v>
       </c>
       <c r="F22" s="25">
         <v>1</v>
       </c>
-      <c r="G22" s="30">
-        <v>10</v>
-      </c>
-      <c r="H22" s="30">
-        <v>10</v>
-      </c>
-      <c r="I22" s="30">
-        <v>10</v>
-      </c>
-      <c r="J22" s="30">
-        <v>10</v>
-      </c>
-      <c r="K22" s="30">
-        <v>10</v>
-      </c>
-      <c r="L22" s="30">
-        <v>10</v>
-      </c>
-      <c r="M22" s="30">
-        <v>10</v>
+      <c r="G22" s="28">
+        <f t="shared" ref="G22:M22" si="2">$S$22*U22</f>
+        <v>80.63549208000002</v>
+      </c>
+      <c r="H22" s="28">
+        <f t="shared" si="2"/>
+        <v>120.95323812000001</v>
+      </c>
+      <c r="I22" s="28">
+        <f t="shared" si="2"/>
+        <v>1007.9436510000002</v>
+      </c>
+      <c r="J22" s="28">
+        <f t="shared" si="2"/>
+        <v>1209.5323812000001</v>
+      </c>
+      <c r="K22" s="28">
+        <f t="shared" si="2"/>
+        <v>1411.1211114000002</v>
+      </c>
+      <c r="L22" s="28">
+        <f t="shared" si="2"/>
+        <v>1511.9154765000003</v>
+      </c>
+      <c r="M22" s="28">
+        <f t="shared" si="2"/>
+        <v>1612.7098416000003</v>
       </c>
       <c r="N22" s="25">
         <v>5</v>
       </c>
       <c r="O22" s="25" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="S22" s="34">
+        <v>2015.8873020000003</v>
+      </c>
+      <c r="T22" s="34"/>
+      <c r="U22" s="36">
+        <v>0.04</v>
+      </c>
+      <c r="V22" s="36">
+        <v>0.06</v>
+      </c>
+      <c r="W22" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="X22" s="36">
+        <v>0.6</v>
+      </c>
+      <c r="Y22" s="36">
+        <v>0.7</v>
+      </c>
+      <c r="Z22" s="36">
+        <v>0.75</v>
+      </c>
+      <c r="AA22" s="36">
+        <v>0.8</v>
       </c>
     </row>
-    <row r="23" spans="2:18">
+    <row r="23" spans="2:27" ht="39.75" customHeight="1">
       <c r="B23" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" t="s">
-        <v>65</v>
-      </c>
-      <c r="D23" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="E23" s="28" t="s">
-        <v>31</v>
+        <v>50</v>
+      </c>
+      <c r="C23" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>68</v>
       </c>
       <c r="F23" s="25">
         <v>1</v>
       </c>
-      <c r="G23" s="30">
-        <v>10</v>
-      </c>
-      <c r="H23" s="30">
-        <v>10</v>
-      </c>
-      <c r="I23" s="30">
-        <v>10</v>
-      </c>
-      <c r="J23" s="30">
-        <v>10</v>
-      </c>
-      <c r="K23" s="30">
-        <v>10</v>
-      </c>
-      <c r="L23" s="30">
-        <v>10</v>
-      </c>
-      <c r="M23" s="30">
-        <v>10</v>
+      <c r="G23" s="28">
+        <f t="shared" ref="G23:M23" si="3">$S$23*U23</f>
+        <v>1.2376653795000001</v>
+      </c>
+      <c r="H23" s="28">
+        <f t="shared" si="3"/>
+        <v>2.4753307590000002</v>
+      </c>
+      <c r="I23" s="28">
+        <f t="shared" si="3"/>
+        <v>43.318288282499999</v>
+      </c>
+      <c r="J23" s="28">
+        <f t="shared" si="3"/>
+        <v>55.694942077500009</v>
+      </c>
+      <c r="K23" s="28">
+        <f t="shared" si="3"/>
+        <v>68.071595872500012</v>
+      </c>
+      <c r="L23" s="28">
+        <f t="shared" si="3"/>
+        <v>74.259922770000003</v>
+      </c>
+      <c r="M23" s="28">
+        <f t="shared" si="3"/>
+        <v>80.448249667500008</v>
       </c>
       <c r="N23" s="25">
         <v>5</v>
       </c>
       <c r="O23" s="25" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="S23" s="34">
+        <v>123.76653795000001</v>
+      </c>
+      <c r="T23" s="34"/>
+      <c r="U23" s="36">
+        <v>0.01</v>
+      </c>
+      <c r="V23" s="36">
+        <v>0.02</v>
+      </c>
+      <c r="W23" s="36">
+        <v>0.35</v>
+      </c>
+      <c r="X23" s="36">
+        <v>0.45</v>
+      </c>
+      <c r="Y23" s="36">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="Z23" s="36">
+        <v>0.6</v>
+      </c>
+      <c r="AA23" s="36">
+        <v>0.65</v>
       </c>
     </row>
-    <row r="24" spans="2:18">
+    <row r="24" spans="2:27" ht="39.75" customHeight="1">
       <c r="B24" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="E24" s="28" t="s">
-        <v>31</v>
+        <v>51</v>
+      </c>
+      <c r="C24" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>68</v>
       </c>
       <c r="F24" s="25">
         <v>1</v>
       </c>
-      <c r="G24" s="30">
-        <v>10</v>
-      </c>
-      <c r="H24" s="30">
-        <v>10</v>
-      </c>
-      <c r="I24" s="30">
-        <v>10</v>
-      </c>
-      <c r="J24" s="30">
-        <v>10</v>
-      </c>
-      <c r="K24" s="30">
-        <v>10</v>
-      </c>
-      <c r="L24" s="30">
-        <v>10</v>
-      </c>
-      <c r="M24" s="30">
-        <v>10</v>
+      <c r="G24" s="28">
+        <f t="shared" ref="G24:M24" si="4">$S$24*U24</f>
+        <v>18.339469302000001</v>
+      </c>
+      <c r="H24" s="28">
+        <f t="shared" si="4"/>
+        <v>27.509203953000004</v>
+      </c>
+      <c r="I24" s="28">
+        <f t="shared" si="4"/>
+        <v>412.63805929500006</v>
+      </c>
+      <c r="J24" s="28">
+        <f t="shared" si="4"/>
+        <v>504.33540580500011</v>
+      </c>
+      <c r="K24" s="28">
+        <f t="shared" si="4"/>
+        <v>596.03275231500004</v>
+      </c>
+      <c r="L24" s="28">
+        <f t="shared" si="4"/>
+        <v>641.88142557000003</v>
+      </c>
+      <c r="M24" s="28">
+        <f t="shared" si="4"/>
+        <v>687.73009882500014</v>
       </c>
       <c r="N24" s="25">
         <v>5</v>
       </c>
       <c r="O24" s="25" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="S24" s="34">
+        <v>916.97346510000011</v>
+      </c>
+      <c r="T24" s="34"/>
+      <c r="U24" s="36">
+        <v>0.02</v>
+      </c>
+      <c r="V24" s="36">
+        <v>0.03</v>
+      </c>
+      <c r="W24" s="36">
+        <v>0.45</v>
+      </c>
+      <c r="X24" s="36">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="Y24" s="36">
+        <v>0.65</v>
+      </c>
+      <c r="Z24" s="36">
+        <v>0.7</v>
+      </c>
+      <c r="AA24" s="36">
+        <v>0.75</v>
       </c>
     </row>
-    <row r="25" spans="2:18">
+    <row r="25" spans="2:27" ht="39.75" customHeight="1">
       <c r="B25" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="C25" t="s">
-        <v>65</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="E25" s="28" t="s">
-        <v>31</v>
+        <v>52</v>
+      </c>
+      <c r="C25" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" s="27" t="s">
+        <v>68</v>
       </c>
       <c r="F25" s="25">
         <v>1</v>
       </c>
-      <c r="G25" s="30">
-        <v>10</v>
-      </c>
-      <c r="H25" s="30">
-        <v>10</v>
-      </c>
-      <c r="I25" s="30">
-        <v>10</v>
-      </c>
-      <c r="J25" s="30">
-        <v>10</v>
-      </c>
-      <c r="K25" s="30">
-        <v>10</v>
-      </c>
-      <c r="L25" s="30">
-        <v>10</v>
-      </c>
-      <c r="M25" s="30">
-        <v>10</v>
+      <c r="G25" s="28">
+        <f t="shared" ref="G25:M25" si="5">$S$25*U25</f>
+        <v>2.9903295674999999</v>
+      </c>
+      <c r="H25" s="28">
+        <f t="shared" si="5"/>
+        <v>5.9806591349999998</v>
+      </c>
+      <c r="I25" s="28">
+        <f t="shared" si="5"/>
+        <v>104.66153486249999</v>
+      </c>
+      <c r="J25" s="28">
+        <f t="shared" si="5"/>
+        <v>134.5648305375</v>
+      </c>
+      <c r="K25" s="28">
+        <f t="shared" si="5"/>
+        <v>164.46812621250001</v>
+      </c>
+      <c r="L25" s="28">
+        <f t="shared" si="5"/>
+        <v>179.41977404999997</v>
+      </c>
+      <c r="M25" s="28">
+        <f t="shared" si="5"/>
+        <v>194.37142188749999</v>
       </c>
       <c r="N25" s="25">
         <v>5</v>
       </c>
       <c r="O25" s="25" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="S25" s="34">
+        <v>299.03295674999998</v>
+      </c>
+      <c r="T25" s="34"/>
+      <c r="U25" s="36">
+        <v>0.01</v>
+      </c>
+      <c r="V25" s="36">
+        <v>0.02</v>
+      </c>
+      <c r="W25" s="36">
+        <v>0.35</v>
+      </c>
+      <c r="X25" s="36">
+        <v>0.45</v>
+      </c>
+      <c r="Y25" s="36">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="Z25" s="36">
+        <v>0.6</v>
+      </c>
+      <c r="AA25" s="36">
+        <v>0.65</v>
       </c>
     </row>
-    <row r="26" spans="2:18">
+    <row r="26" spans="2:27" ht="39.75" customHeight="1">
       <c r="B26" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="E26" s="28" t="s">
-        <v>31</v>
+        <v>53</v>
+      </c>
+      <c r="C26" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="E26" s="27" t="s">
+        <v>68</v>
       </c>
       <c r="F26" s="25">
         <v>1</v>
       </c>
-      <c r="G26" s="30">
-        <v>10</v>
-      </c>
-      <c r="H26" s="30">
-        <v>10</v>
-      </c>
-      <c r="I26" s="30">
-        <v>10</v>
-      </c>
-      <c r="J26" s="30">
-        <v>10</v>
-      </c>
-      <c r="K26" s="30">
-        <v>10</v>
-      </c>
-      <c r="L26" s="30">
-        <v>10</v>
-      </c>
-      <c r="M26" s="30">
-        <v>10</v>
+      <c r="G26" s="28">
+        <f t="shared" ref="G26:M26" si="6">$S$26*U26</f>
+        <v>44.182134646000002</v>
+      </c>
+      <c r="H26" s="28">
+        <f t="shared" si="6"/>
+        <v>66.273201968999999</v>
+      </c>
+      <c r="I26" s="28">
+        <f t="shared" si="6"/>
+        <v>883.64269292000017</v>
+      </c>
+      <c r="J26" s="28">
+        <f t="shared" si="6"/>
+        <v>1104.5533661500001</v>
+      </c>
+      <c r="K26" s="28">
+        <f t="shared" si="6"/>
+        <v>1325.46403938</v>
+      </c>
+      <c r="L26" s="28">
+        <f t="shared" si="6"/>
+        <v>1435.9193759950001</v>
+      </c>
+      <c r="M26" s="28">
+        <f t="shared" si="6"/>
+        <v>1546.37471261</v>
       </c>
       <c r="N26" s="25">
         <v>5</v>
       </c>
       <c r="O26" s="25" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="S26" s="34">
+        <v>2209.1067323000002</v>
+      </c>
+      <c r="T26" s="34"/>
+      <c r="U26" s="36">
+        <v>0.02</v>
+      </c>
+      <c r="V26" s="36">
+        <v>0.03</v>
+      </c>
+      <c r="W26" s="36">
+        <v>0.4</v>
+      </c>
+      <c r="X26" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="Y26" s="36">
+        <v>0.6</v>
+      </c>
+      <c r="Z26" s="36">
+        <v>0.65</v>
+      </c>
+      <c r="AA26" s="36">
+        <v>0.7</v>
       </c>
     </row>
-    <row r="27" spans="2:18">
+    <row r="27" spans="2:27" ht="39.75" customHeight="1">
       <c r="B27" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="C27" t="s">
-        <v>65</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="E27" s="28" t="s">
-        <v>31</v>
+        <v>54</v>
+      </c>
+      <c r="C27" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="E27" s="27" t="s">
+        <v>68</v>
       </c>
       <c r="F27" s="25">
         <v>1</v>
       </c>
-      <c r="G27" s="30">
-        <v>1</v>
-      </c>
-      <c r="H27" s="30">
-        <v>1</v>
-      </c>
-      <c r="I27" s="30">
-        <v>1</v>
-      </c>
-      <c r="J27" s="30">
-        <v>1</v>
-      </c>
-      <c r="K27" s="30">
-        <v>1</v>
-      </c>
-      <c r="L27" s="30">
-        <v>1</v>
-      </c>
-      <c r="M27" s="30">
-        <v>1</v>
+      <c r="G27" s="28">
+        <f t="shared" ref="G27:M27" si="7">$S$27*U27</f>
+        <v>0.51994041000000002</v>
+      </c>
+      <c r="H27" s="28">
+        <f t="shared" si="7"/>
+        <v>0.51994041000000002</v>
+      </c>
+      <c r="I27" s="28">
+        <f t="shared" si="7"/>
+        <v>10.3988082</v>
+      </c>
+      <c r="J27" s="28">
+        <f t="shared" si="7"/>
+        <v>15.598212299999998</v>
+      </c>
+      <c r="K27" s="28">
+        <f t="shared" si="7"/>
+        <v>20.797616399999999</v>
+      </c>
+      <c r="L27" s="28">
+        <f t="shared" si="7"/>
+        <v>23.39731845</v>
+      </c>
+      <c r="M27" s="28">
+        <f t="shared" si="7"/>
+        <v>25.997020499999998</v>
       </c>
       <c r="N27" s="25">
         <v>5</v>
       </c>
       <c r="O27" s="25" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="S27" s="34">
+        <v>51.994040999999996</v>
+      </c>
+      <c r="T27" s="34"/>
+      <c r="U27" s="36">
+        <v>0.01</v>
+      </c>
+      <c r="V27" s="36">
+        <v>0.01</v>
+      </c>
+      <c r="W27" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="X27" s="36">
+        <v>0.3</v>
+      </c>
+      <c r="Y27" s="36">
+        <v>0.4</v>
+      </c>
+      <c r="Z27" s="36">
+        <v>0.45</v>
+      </c>
+      <c r="AA27" s="36">
+        <v>0.5</v>
       </c>
     </row>
-    <row r="28" spans="2:18">
+    <row r="28" spans="2:27" ht="39.75" customHeight="1">
       <c r="B28" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" t="s">
-        <v>65</v>
+        <v>55</v>
+      </c>
+      <c r="C28" s="37" t="s">
+        <v>70</v>
       </c>
       <c r="D28" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="E28" s="28" t="s">
-        <v>31</v>
+      <c r="E28" s="27" t="s">
+        <v>68</v>
       </c>
       <c r="F28" s="25">
         <v>1</v>
       </c>
-      <c r="G28" s="30">
-        <v>10</v>
-      </c>
-      <c r="H28" s="30">
-        <v>10</v>
-      </c>
-      <c r="I28" s="30">
-        <v>10</v>
-      </c>
-      <c r="J28" s="30">
-        <v>10</v>
-      </c>
-      <c r="K28" s="30">
-        <v>10</v>
-      </c>
-      <c r="L28" s="30">
-        <v>10</v>
-      </c>
-      <c r="M28" s="30">
-        <v>10</v>
+      <c r="G28" s="28">
+        <f t="shared" ref="G28:M28" si="8">$S$28*U28</f>
+        <v>1192.1976166000002</v>
+      </c>
+      <c r="H28" s="28">
+        <f t="shared" si="8"/>
+        <v>1490.24702075</v>
+      </c>
+      <c r="I28" s="28">
+        <f t="shared" si="8"/>
+        <v>7451.2351037500002</v>
+      </c>
+      <c r="J28" s="28">
+        <f t="shared" si="8"/>
+        <v>9686.6056348750008</v>
+      </c>
+      <c r="K28" s="28">
+        <f t="shared" si="8"/>
+        <v>11176.852655625</v>
+      </c>
+      <c r="L28" s="28">
+        <f t="shared" si="8"/>
+        <v>12667.099676375001</v>
+      </c>
+      <c r="M28" s="28">
+        <f t="shared" si="8"/>
+        <v>13412.223186750001</v>
       </c>
       <c r="N28" s="25">
         <v>5</v>
       </c>
       <c r="O28" s="25" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="S28" s="34">
+        <v>14902.4702075</v>
+      </c>
+      <c r="T28" s="34"/>
+      <c r="U28" s="36">
+        <v>0.08</v>
+      </c>
+      <c r="V28" s="36">
+        <v>0.1</v>
+      </c>
+      <c r="W28" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="X28" s="36">
+        <v>0.65</v>
+      </c>
+      <c r="Y28" s="36">
+        <v>0.75</v>
+      </c>
+      <c r="Z28" s="36">
+        <v>0.85</v>
+      </c>
+      <c r="AA28" s="36">
+        <v>0.9</v>
       </c>
     </row>
-    <row r="29" spans="2:18">
+    <row r="29" spans="2:27" ht="39.75" customHeight="1">
       <c r="B29" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" t="s">
-        <v>65</v>
-      </c>
-      <c r="D29" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="E29" s="28" t="s">
-        <v>31</v>
+      <c r="E29" s="27" t="s">
+        <v>68</v>
       </c>
       <c r="F29" s="25">
         <v>1</v>
       </c>
-      <c r="G29" s="30">
-        <v>10</v>
-      </c>
-      <c r="H29" s="30">
-        <v>10</v>
-      </c>
-      <c r="I29" s="30">
-        <v>10</v>
-      </c>
-      <c r="J29" s="30">
-        <v>10</v>
-      </c>
-      <c r="K29" s="30">
-        <v>10</v>
-      </c>
-      <c r="L29" s="30">
-        <v>10</v>
-      </c>
-      <c r="M29" s="30">
-        <v>10</v>
+      <c r="G29" s="28">
+        <f t="shared" ref="G29:M29" si="9">$S$29*U29</f>
+        <v>720.69891695999991</v>
+      </c>
+      <c r="H29" s="28">
+        <f t="shared" si="9"/>
+        <v>960.93188927999995</v>
+      </c>
+      <c r="I29" s="28">
+        <f t="shared" si="9"/>
+        <v>5405.2418771999992</v>
+      </c>
+      <c r="J29" s="28">
+        <f t="shared" si="9"/>
+        <v>7206.9891695999986</v>
+      </c>
+      <c r="K29" s="28">
+        <f t="shared" si="9"/>
+        <v>8408.1540311999979</v>
+      </c>
+      <c r="L29" s="28">
+        <f t="shared" si="9"/>
+        <v>9609.3188928</v>
+      </c>
+      <c r="M29" s="28">
+        <f t="shared" si="9"/>
+        <v>10209.901323599999</v>
       </c>
       <c r="N29" s="25">
         <v>5</v>
       </c>
       <c r="O29" s="25" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="S29" s="34">
+        <v>12011.648615999999</v>
+      </c>
+      <c r="T29" s="34"/>
+      <c r="U29" s="36">
+        <v>0.06</v>
+      </c>
+      <c r="V29" s="36">
+        <v>0.08</v>
+      </c>
+      <c r="W29" s="36">
+        <v>0.45</v>
+      </c>
+      <c r="X29" s="36">
+        <v>0.6</v>
+      </c>
+      <c r="Y29" s="36">
+        <v>0.7</v>
+      </c>
+      <c r="Z29" s="36">
+        <v>0.8</v>
+      </c>
+      <c r="AA29" s="36">
+        <v>0.85</v>
       </c>
     </row>
-    <row r="30" spans="2:18">
+    <row r="30" spans="2:27" ht="39.75" customHeight="1">
       <c r="B30" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" t="s">
-        <v>65</v>
-      </c>
-      <c r="D30" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="E30" s="28" t="s">
-        <v>31</v>
+        <v>57</v>
+      </c>
+      <c r="C30" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" s="27" t="s">
+        <v>68</v>
       </c>
       <c r="F30" s="25">
         <v>1</v>
       </c>
-      <c r="G30" s="30">
-        <v>10</v>
-      </c>
-      <c r="H30" s="30">
-        <v>10</v>
-      </c>
-      <c r="I30" s="30">
-        <v>10</v>
-      </c>
-      <c r="J30" s="30">
-        <v>10</v>
-      </c>
-      <c r="K30" s="30">
-        <v>10</v>
-      </c>
-      <c r="L30" s="30">
-        <v>10</v>
-      </c>
-      <c r="M30" s="30">
-        <v>10</v>
+      <c r="G30" s="28">
+        <f t="shared" ref="G30:M30" si="10">$S$30*U30</f>
+        <v>937.78322500000002</v>
+      </c>
+      <c r="H30" s="28">
+        <f t="shared" si="10"/>
+        <v>1125.3398699999998</v>
+      </c>
+      <c r="I30" s="28">
+        <f t="shared" si="10"/>
+        <v>5157.8077375000003</v>
+      </c>
+      <c r="J30" s="28">
+        <f t="shared" si="10"/>
+        <v>6564.4825749999991</v>
+      </c>
+      <c r="K30" s="28">
+        <f t="shared" si="10"/>
+        <v>7502.2658000000001</v>
+      </c>
+      <c r="L30" s="28">
+        <f t="shared" si="10"/>
+        <v>8440.0490250000003</v>
+      </c>
+      <c r="M30" s="28">
+        <f t="shared" si="10"/>
+        <v>8908.9406374999999</v>
       </c>
       <c r="N30" s="25">
         <v>5</v>
       </c>
       <c r="O30" s="25" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="S30" s="34">
+        <v>9377.8322499999995</v>
+      </c>
+      <c r="T30" s="34"/>
+      <c r="U30" s="36">
+        <v>0.1</v>
+      </c>
+      <c r="V30" s="36">
+        <v>0.12</v>
+      </c>
+      <c r="W30" s="36">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="X30" s="36">
+        <v>0.7</v>
+      </c>
+      <c r="Y30" s="36">
+        <v>0.8</v>
+      </c>
+      <c r="Z30" s="36">
+        <v>0.9</v>
+      </c>
+      <c r="AA30" s="36">
+        <v>0.95</v>
       </c>
     </row>
-    <row r="31" spans="2:18">
+    <row r="31" spans="2:27" ht="39.75" customHeight="1">
       <c r="B31" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" t="s">
-        <v>65</v>
-      </c>
-      <c r="D31" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="E31" s="28" t="s">
-        <v>31</v>
+        <v>58</v>
+      </c>
+      <c r="C31" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="D31" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="27" t="s">
+        <v>68</v>
       </c>
       <c r="F31" s="25">
         <v>1</v>
       </c>
-      <c r="G31" s="30">
-        <v>10</v>
-      </c>
-      <c r="H31" s="30">
-        <v>10</v>
-      </c>
-      <c r="I31" s="30">
-        <v>10</v>
-      </c>
-      <c r="J31" s="30">
-        <v>10</v>
-      </c>
-      <c r="K31" s="30">
-        <v>10</v>
-      </c>
-      <c r="L31" s="30">
-        <v>10</v>
-      </c>
-      <c r="M31" s="30">
-        <v>10</v>
+      <c r="G31" s="28">
+        <f t="shared" ref="G31:M31" si="11">$S$31*U31</f>
+        <v>161.31754440000003</v>
+      </c>
+      <c r="H31" s="28">
+        <f t="shared" si="11"/>
+        <v>215.09005920000004</v>
+      </c>
+      <c r="I31" s="28">
+        <f t="shared" si="11"/>
+        <v>1344.3128700000002</v>
+      </c>
+      <c r="J31" s="28">
+        <f t="shared" si="11"/>
+        <v>1747.6067310000003</v>
+      </c>
+      <c r="K31" s="28">
+        <f t="shared" si="11"/>
+        <v>2016.4693050000003</v>
+      </c>
+      <c r="L31" s="28">
+        <f t="shared" si="11"/>
+        <v>2285.3318790000003</v>
+      </c>
+      <c r="M31" s="28">
+        <f t="shared" si="11"/>
+        <v>2419.7631660000006</v>
       </c>
       <c r="N31" s="25">
         <v>5</v>
       </c>
       <c r="O31" s="25" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="S31" s="34">
+        <v>2688.6257400000004</v>
+      </c>
+      <c r="T31" s="34"/>
+      <c r="U31" s="36">
+        <v>0.06</v>
+      </c>
+      <c r="V31" s="36">
+        <v>0.08</v>
+      </c>
+      <c r="W31" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="X31" s="36">
+        <v>0.65</v>
+      </c>
+      <c r="Y31" s="36">
+        <v>0.75</v>
+      </c>
+      <c r="Z31" s="36">
+        <v>0.85</v>
+      </c>
+      <c r="AA31" s="36">
+        <v>0.9</v>
       </c>
     </row>
-    <row r="45" spans="18:18">
+    <row r="33" spans="18:21">
+      <c r="U33" s="29"/>
+    </row>
+    <row r="34" spans="18:21">
+      <c r="U34" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45" spans="18:21">
       <c r="R45" s="13"/>
     </row>
     <row r="74" spans="3:17" ht="15.75" thickBot="1"/>
     <row r="75" spans="3:17">
       <c r="D75" s="10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>17</v>
@@ -7775,7 +8240,7 @@
       <c r="C77" s="11"/>
       <c r="D77" s="11"/>
       <c r="E77" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F77" s="11"/>
       <c r="G77" s="11"/>
@@ -7796,7 +8261,7 @@
       <c r="C78" s="12"/>
       <c r="D78" s="12"/>
       <c r="E78" s="12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F78" s="12"/>
       <c r="G78" s="12"/>
@@ -7817,7 +8282,7 @@
       <c r="C79" s="11"/>
       <c r="D79" s="11"/>
       <c r="E79" s="11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F79" s="11"/>
       <c r="G79" s="11"/>
@@ -7838,7 +8303,7 @@
       <c r="C80" s="12"/>
       <c r="D80" s="12"/>
       <c r="E80" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F80" s="12"/>
       <c r="G80" s="12"/>
@@ -7859,7 +8324,7 @@
       <c r="C81" s="11"/>
       <c r="D81" s="11"/>
       <c r="E81" s="11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F81" s="11"/>
       <c r="G81" s="11"/>
@@ -7880,7 +8345,7 @@
       <c r="C82" s="12"/>
       <c r="D82" s="12"/>
       <c r="E82" s="12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F82" s="12"/>
       <c r="G82" s="12"/>
@@ -7901,7 +8366,7 @@
       <c r="C83" s="11"/>
       <c r="D83" s="11"/>
       <c r="E83" s="11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F83" s="11"/>
       <c r="G83" s="11"/>
@@ -7912,7 +8377,6 @@
       <c r="L83" s="11"/>
       <c r="M83" s="11"/>
       <c r="N83" s="11"/>
-      <c r="O83" s="11"/>
       <c r="P83" s="11">
         <v>0.22799999999999998</v>
       </c>
@@ -7922,7 +8386,7 @@
       <c r="C84" s="12"/>
       <c r="D84" s="12"/>
       <c r="E84" s="12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F84" s="12"/>
       <c r="G84" s="12"/>
@@ -7940,8 +8404,9 @@
       <c r="Q84" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="G19:I19"/>
+    <mergeCell ref="U18:AA18"/>
   </mergeCells>
   <phoneticPr fontId="114" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8214,7 +8679,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD4F0E47-7F06-4CD3-9EF5-74801E072FF2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{036DCD33-36A5-47D0-98BE-9E2AAEA5C5D8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -8243,10 +8708,16 @@
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31CAF8EB-1589-42DD-BC0B-7BF2AA67CCF9}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
-    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/SuppXLS/Scen_InputsBiogPlant.xlsx
+++ b/SuppXLS/Scen_InputsBiogPlant.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aghedupl.sharepoint.com/sites/TIMES-PL-PSE/Shared Documents/General/MODELE/2026/AGR_wyizolowany/SuppXLS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="202" documentId="13_ncr:1_{D1555BA4-DD4C-4A63-B1C1-C1C118AFF6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D773A174-B533-4A50-B989-C00D416BF573}"/>
+  <xr:revisionPtr revIDLastSave="205" documentId="13_ncr:1_{D1555BA4-DD4C-4A63-B1C1-C1C118AFF6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69D3D59D-5FAC-4099-9B92-6778A142520C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UCT1" sheetId="1" r:id="rId1"/>
@@ -5253,7 +5253,6 @@
     <cellStyle name="Neutralne 9_COM_BND" xfId="1079" xr:uid="{6A2CB00B-A082-4E91-9034-E18742ED0AD0}"/>
     <cellStyle name="Neutralne_CHP" xfId="1080" xr:uid="{D4B1577A-56D8-4830-B45D-ACB712881634}"/>
     <cellStyle name="no dec" xfId="1081" xr:uid="{05A6E796-705C-459C-9083-31C5C2B501A7}"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal - Style1" xfId="1082" xr:uid="{422DB56D-DE92-449A-A73B-E02EC79F0146}"/>
     <cellStyle name="Normal - Style1 2 2 3" xfId="14" xr:uid="{DC545E0B-E419-471E-892E-F5E9CBF5B7CC}"/>
     <cellStyle name="Normal - Style1 2 2 3 2" xfId="2168" xr:uid="{B3B665C3-72E1-4DCC-90DC-397510F65D65}"/>
@@ -5327,6 +5326,7 @@
     <cellStyle name="Normal GHG-Shade 2" xfId="1129" xr:uid="{332E491B-28EA-478D-8837-B4DC72CD947A}"/>
     <cellStyle name="Normale_B2020" xfId="1130" xr:uid="{BBE33778-D881-4D14-9174-CBFFF9C5A0A1}"/>
     <cellStyle name="Normale_Scen_UC_IND-StrucConst" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
     <cellStyle name="Normalny 10" xfId="1132" xr:uid="{7BEE2132-44C2-4E67-A38F-4476F86FD93C}"/>
     <cellStyle name="Normalny 10 10" xfId="11" xr:uid="{3C7998C5-C4B0-42D6-B1DA-0233E04A4AA3}"/>
     <cellStyle name="Normalny 10 10 2" xfId="2167" xr:uid="{A7EB448A-69A2-4460-B07D-C674E4A16132}"/>
@@ -6704,7 +6704,7 @@
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Pakiet Office 2007–2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6742,7 +6742,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Pakiet Office 2007–2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -6814,7 +6814,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Pakiet Office 2007–2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -7813,11 +7813,11 @@
       </c>
       <c r="G27" s="28">
         <f t="shared" ref="G27:M27" si="7">$S$27*U27</f>
-        <v>0.51994041000000002</v>
+        <v>0.46794636899999992</v>
       </c>
       <c r="H27" s="28">
         <f t="shared" si="7"/>
-        <v>0.51994041000000002</v>
+        <v>0.46794636899999992</v>
       </c>
       <c r="I27" s="28">
         <f t="shared" si="7"/>
@@ -7850,10 +7850,10 @@
       </c>
       <c r="T27" s="34"/>
       <c r="U27" s="36">
-        <v>0.01</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="V27" s="36">
-        <v>0.01</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="W27" s="36">
         <v>0.2</v>
@@ -8416,8 +8416,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A7D98A4600D5044F9F854C890D6CC50E" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3a89f9027361f7d3c140af2fe110eadb">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8acd6055-54fc-4ce7-b3df-0a09834a0329" xmlns:ns3="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff995f4215d3ca90fb464d6ddf93df71" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100A7D98A4600D5044F9F854C890D6CC50E" ma:contentTypeVersion="16" ma:contentTypeDescription="Utwórz nowy dokument." ma:contentTypeScope="" ma:versionID="d5167bf0dd55feede3e29f1a430471b5">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8acd6055-54fc-4ce7-b3df-0a09834a0329" xmlns:ns3="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="24bde18039da748f015df48b5e1e3648" ns2:_="" ns3:_="">
     <xsd:import namespace="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
     <xsd:import namespace="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
     <xsd:element name="properties">
@@ -8461,7 +8461,7 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="11" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="b7b31e59-74a4-4436-bc03-9931855e0d9a" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="11" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Tagi obrazów" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="b7b31e59-74a4-4436-bc03-9931855e0d9a" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -8532,7 +8532,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Udostępnianie" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -8551,7 +8551,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Udostępnione dla — szczegóły" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -8568,8 +8568,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Typ zawartości"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Tytuł"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -8659,15 +8659,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
@@ -8678,46 +8669,40 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{036DCD33-36A5-47D0-98BE-9E2AAEA5C5D8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A0A6CDD-7502-4A1B-904B-A464B45B7A5E}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31CAF8EB-1589-42DD-BC0B-7BF2AA67CCF9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
-    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A411E4B2-5D3D-4AF5-AF43-FAF4CEAEDF56}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31CAF8EB-1589-42DD-BC0B-7BF2AA67CCF9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/SuppXLS/Scen_InputsBiogPlant.xlsx
+++ b/SuppXLS/Scen_InputsBiogPlant.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aghedupl.sharepoint.com/sites/TIMES-PL-PSE/Shared Documents/General/MODELE/2026/AGR_wyizolowany/SuppXLS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="205" documentId="13_ncr:1_{D1555BA4-DD4C-4A63-B1C1-C1C118AFF6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69D3D59D-5FAC-4099-9B92-6778A142520C}"/>
+  <xr:revisionPtr revIDLastSave="207" documentId="13_ncr:1_{D1555BA4-DD4C-4A63-B1C1-C1C118AFF6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C00612FB-1C72-441F-A459-A1B358D9F2B6}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UCT1" sheetId="1" r:id="rId1"/>
@@ -7813,11 +7813,11 @@
       </c>
       <c r="G27" s="28">
         <f t="shared" ref="G27:M27" si="7">$S$27*U27</f>
-        <v>0.46794636899999992</v>
+        <v>1.03988082</v>
       </c>
       <c r="H27" s="28">
         <f t="shared" si="7"/>
-        <v>0.46794636899999992</v>
+        <v>1.03988082</v>
       </c>
       <c r="I27" s="28">
         <f t="shared" si="7"/>
@@ -7850,10 +7850,10 @@
       </c>
       <c r="T27" s="34"/>
       <c r="U27" s="36">
-        <v>8.9999999999999993E-3</v>
+        <v>0.02</v>
       </c>
       <c r="V27" s="36">
-        <v>8.9999999999999993E-3</v>
+        <v>0.02</v>
       </c>
       <c r="W27" s="36">
         <v>0.2</v>
@@ -8659,6 +8659,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
@@ -8669,40 +8678,31 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A0A6CDD-7502-4A1B-904B-A464B45B7A5E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{683255CD-97AB-4383-A5D5-7942FDB774C7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31CAF8EB-1589-42DD-BC0B-7BF2AA67CCF9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A411E4B2-5D3D-4AF5-AF43-FAF4CEAEDF56}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A411E4B2-5D3D-4AF5-AF43-FAF4CEAEDF56}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31CAF8EB-1589-42DD-BC0B-7BF2AA67CCF9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>